--- a/astro-site/public/dl/guia-churreria-chocolateria/turnos-plantilla-y-madrugada.xlsx
+++ b/astro-site/public/dl/guia-churreria-chocolateria/turnos-plantilla-y-madrugada.xlsx
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B65" s="21">
         <f>'Coste de Plantilla'!$B$19</f>
-        <v>13.243842884413233</v>
+        <v>13.243842884413235</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B66" s="22">
         <f>IFERROR(ABS('Parámetros'!$B$9/B65-1),"")</f>
-        <v>2.220446049250313e-16</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C66" t="inlineStr"/>
     </row>
@@ -10330,11 +10330,11 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="5">
+    <mergeCell ref="S62:Y62"/>
+    <mergeCell ref="K62:Q62"/>
+    <mergeCell ref="C62:I62"/>
     <mergeCell ref="B9:F9"/>
-    <mergeCell ref="C62:I62"/>
-    <mergeCell ref="S62:Y62"/>
     <mergeCell ref="AA62:AG62"/>
-    <mergeCell ref="K62:Q62"/>
   </mergeCells>
   <conditionalFormatting sqref="B9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
@@ -12040,11 +12040,11 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="5">
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="A16:N16"/>
     <mergeCell ref="A15:N15"/>
     <mergeCell ref="A14:N14"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="A16:N16"/>
   </mergeCells>
   <conditionalFormatting sqref="G8">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="L5" s="36">
         <f>B25</f>
-        <v>119350.20111361095</v>
+        <v>119350.20111361096</v>
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
@@ -12662,11 +12662,11 @@
       </c>
       <c r="M14" s="41">
         <f>SUM(M9:M13)</f>
-        <v>2725.4707549999994</v>
+        <v>2725.470755</v>
       </c>
       <c r="Q14" s="36">
         <f>SUM(Q9:Q13)</f>
-        <v>106083.18150415</v>
+        <v>106083.18150415001</v>
       </c>
     </row>
     <row r="15"/>
@@ -12685,7 +12685,7 @@
       </c>
       <c r="B17" s="41">
         <f>Q14</f>
-        <v>106083.18150415</v>
+        <v>106083.18150415001</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="B19" s="36">
         <f>IFERROR(B17/B18,"")</f>
-        <v>13.243842884413233</v>
+        <v>13.243842884413235</v>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
       </c>
       <c r="B24" s="41">
         <f>(B22+B23)*B19</f>
-        <v>13267.01960946096</v>
+        <v>13267.019609460962</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="B25" s="36">
         <f>B17+B24</f>
-        <v>119350.20111361095</v>
+        <v>119350.20111361096</v>
       </c>
     </row>
     <row r="26"/>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="B14" s="36">
         <f>B13*'Coste de Plantilla'!$B$19</f>
-        <v>8513.898997122793</v>
+        <v>8513.898997122795</v>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
@@ -13671,9 +13671,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
-    <mergeCell ref="B15:C15"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B15:C15"/>
   </mergeCells>
   <conditionalFormatting sqref="B15">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
